--- a/scripts/kindergarten/inputs/kg-teacher-assignment-map.xlsx
+++ b/scripts/kindergarten/inputs/kg-teacher-assignment-map.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3178F0FD-FCCD-4FD9-995B-A9F7119E0D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BDF665B-0CD4-4B7D-B8BE-8D8CADE1E847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="300" windowWidth="19950" windowHeight="13860" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="960" yWindow="8190" windowWidth="15315" windowHeight="7245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="التوزيع" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1332" uniqueCount="226">
   <si>
     <t>schoolId</t>
   </si>
@@ -691,13 +691,25 @@
   </si>
   <si>
     <t>p-r-a-atyar</t>
+  </si>
+  <si>
+    <t>الروضة الأولى</t>
+  </si>
+  <si>
+    <t>d-a-athunian@qz.org.sa</t>
+  </si>
+  <si>
+    <t>p-d-a-athunian</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ديم عبدالله عبدالكريم الثنيان </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -764,6 +776,21 @@
       <family val="2"/>
       <charset val="178"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Google Sans"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF842E2E"/>
+      <name val="Tajawal"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF423671"/>
+      <name val="Tajawal"/>
     </font>
   </fonts>
   <fills count="8">
@@ -890,7 +917,7 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -988,13 +1015,19 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -1337,7 +1370,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.28515625" style="20" bestFit="1" customWidth="1"/>
@@ -1346,7 +1379,7 @@
     <col min="4" max="4" width="13.42578125" style="20" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.5703125" style="20" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20" style="20" customWidth="1"/>
     <col min="8" max="8" width="26.140625" style="20" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="9.140625" style="20"/>
   </cols>
@@ -1375,6 +1408,32 @@
       </c>
       <c r="H1" s="3" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="28.5">
+      <c r="A2" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="35" t="s">
+        <v>223</v>
+      </c>
+      <c r="G2" s="41" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2" s="35" t="s">
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -3897,24 +3956,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="2" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
     </row>
     <row r="3" spans="1:6" ht="27.95" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -5527,13 +5586,13 @@
       <c r="E2" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="35" t="s">
         <v>213</v>
       </c>
       <c r="G2" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="H2" s="37" t="s">
+      <c r="H2" s="35" t="s">
         <v>159</v>
       </c>
     </row>
@@ -5553,13 +5612,13 @@
       <c r="E3" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="35" t="s">
         <v>213</v>
       </c>
       <c r="G3" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="H3" s="37" t="s">
+      <c r="H3" s="35" t="s">
         <v>159</v>
       </c>
     </row>
@@ -5579,13 +5638,13 @@
       <c r="E4" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="37" t="s">
+      <c r="F4" s="35" t="s">
         <v>213</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="H4" s="37" t="s">
+      <c r="H4" s="35" t="s">
         <v>159</v>
       </c>
     </row>
@@ -5605,13 +5664,13 @@
       <c r="E5" s="20" t="s">
         <v>175</v>
       </c>
-      <c r="F5" s="37" t="s">
+      <c r="F5" s="35" t="s">
         <v>213</v>
       </c>
       <c r="G5" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="H5" s="37" t="s">
+      <c r="H5" s="35" t="s">
         <v>159</v>
       </c>
     </row>
@@ -5631,13 +5690,13 @@
       <c r="E6" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="35" t="s">
         <v>213</v>
       </c>
       <c r="G6" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="H6" s="37" t="s">
+      <c r="H6" s="35" t="s">
         <v>159</v>
       </c>
     </row>
@@ -5657,13 +5716,13 @@
       <c r="E7" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="F7" s="37" t="s">
+      <c r="F7" s="35" t="s">
         <v>213</v>
       </c>
       <c r="G7" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="H7" s="37" t="s">
+      <c r="H7" s="35" t="s">
         <v>159</v>
       </c>
     </row>

--- a/scripts/kindergarten/inputs/kg-teacher-assignment-map.xlsx
+++ b/scripts/kindergarten/inputs/kg-teacher-assignment-map.xlsx
@@ -5,7 +5,7 @@
   <workbookPr filterPrivacy="1"/>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BDF665B-0CD4-4B7D-B8BE-8D8CADE1E847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="8190" windowWidth="15315" windowHeight="7245" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="960" yWindow="7095" windowWidth="18690" windowHeight="8340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="التوزيع" sheetId="1" r:id="rId1"/>
@@ -1016,18 +1016,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -1411,7 +1411,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="28.5">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="36" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="20" t="s">
@@ -1420,16 +1420,16 @@
       <c r="C2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="E2" s="37" t="s">
         <v>12</v>
       </c>
       <c r="F2" s="35" t="s">
         <v>223</v>
       </c>
-      <c r="G2" s="41" t="s">
+      <c r="G2" s="39" t="s">
         <v>224</v>
       </c>
       <c r="H2" s="35" t="s">
@@ -3956,24 +3956,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
     </row>
     <row r="2" spans="1:6" ht="21.95" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
     </row>
     <row r="3" spans="1:6" ht="27.95" customHeight="1">
       <c r="A3" s="1" t="s">
